--- a/product_selector_out/STM32U375-385.xlsx
+++ b/product_selector_out/STM32U375-385.xlsx
@@ -5756,9 +5756,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="9" t="inlineStr">
@@ -6083,9 +6083,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="9" t="inlineStr">
@@ -6410,9 +6410,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="9" t="inlineStr">
@@ -6737,9 +6737,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="9" t="inlineStr">
@@ -7064,9 +7064,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="9" t="inlineStr">
@@ -7391,9 +7391,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="9" t="inlineStr">
@@ -7718,9 +7718,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="9" t="inlineStr">
@@ -8045,9 +8045,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="9" t="inlineStr">
@@ -8372,9 +8372,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="9" t="inlineStr">
@@ -8699,9 +8699,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="9" t="inlineStr">
@@ -9026,9 +9026,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY22" s="9" t="inlineStr">
@@ -9353,9 +9353,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="9" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9586,19 +9586,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32U385VG</t>
+          <t>STM32U385RG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9696,19 +9696,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U385KG</t>
+          <t>STM32U385VG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9718,19 +9718,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U385KG</t>
+          <t>STM32U385VG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9806,19 +9806,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U375KG</t>
+          <t>STM32U385KG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9828,19 +9828,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32U375KG</t>
+          <t>STM32U385KG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9850,19 +9850,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32U375KG</t>
+          <t>STM32U385KG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9894,19 +9894,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9916,19 +9916,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -9938,14 +9938,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9967,7 +9967,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9989,7 +9989,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10011,7 +10011,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10026,19 +10026,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10048,19 +10048,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -10070,19 +10070,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -10092,19 +10092,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -10114,19 +10114,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -10136,19 +10136,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -10158,19 +10158,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10180,19 +10180,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10202,19 +10202,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10224,19 +10224,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10246,19 +10246,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10268,19 +10268,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10290,19 +10290,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10312,19 +10312,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -10334,19 +10334,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -10356,19 +10356,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10378,19 +10378,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10400,14 +10400,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -10422,14 +10422,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -10451,7 +10451,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -10473,7 +10473,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10488,19 +10488,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10510,19 +10510,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10532,19 +10532,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10554,19 +10554,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -10576,19 +10576,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -10598,27 +10598,291 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>STM32U375RE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32U375RE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32U375RE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32U375VE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32U375VE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32U375VE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32U375VE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32U375VE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>STM32U375VG</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32U375VG</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>

--- a/product_selector_out/STM32U375-385.xlsx
+++ b/product_selector_out/STM32U375-385.xlsx
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE18" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE20" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AD21" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE21" s="4" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79, 82</t>
         </is>
       </c>
       <c r="AE22" s="4" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AD23" s="4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79, 82</t>
         </is>
       </c>
       <c r="AE23" s="4" t="inlineStr">
@@ -6592,9 +6592,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
@@ -6919,9 +6919,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
@@ -7246,9 +7246,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
@@ -7573,9 +7573,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
@@ -8227,9 +8227,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
@@ -8554,9 +8554,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
@@ -8881,9 +8881,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
@@ -9208,9 +9208,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">

--- a/product_selector_out/STM32U375-385.xlsx
+++ b/product_selector_out/STM32U375-385.xlsx
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AM16" s="4" t="inlineStr">
         <is>
-          <t>1, 2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN16" s="4" t="inlineStr">
@@ -6682,9 +6682,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -7009,9 +7009,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr">
@@ -7336,9 +7336,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">
@@ -7663,9 +7663,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -8317,9 +8317,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -8644,9 +8644,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -8971,9 +8971,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -9298,9 +9298,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">

--- a/product_selector_out/STM32U375-385.xlsx
+++ b/product_selector_out/STM32U375-385.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM23"/>
+  <dimension ref="A1:BN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.78125" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u385cg.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u385cg.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u385cg.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u385cg.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -4917,12 +4979,17 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -4943,16 +5010,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -4965,6 +5030,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -4984,7 +5050,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -5013,7 +5081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM23"/>
+  <dimension ref="A1:BN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5081,6 +5149,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5414,6 +5483,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -5509,6 +5583,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5831,7 +5906,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6158,7 +6238,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6485,7 +6570,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6812,7 +6902,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7139,7 +7234,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7466,7 +7566,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7793,7 +7898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8120,7 +8230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8447,7 +8562,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8774,7 +8894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9101,7 +9226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9428,7 +9558,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9436,8 +9571,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
